--- a/product-definitions/spreadsheet/ch4-co2-h2o-co-concentration.xlsx
+++ b/product-definitions/spreadsheet/ch4-co2-h2o-co-concentration.xlsx
@@ -282,7 +282,7 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-  <fonts count="8">
+  <fonts count="7">
     <font>
       <sz val="10.0"/>
       <color rgb="FF000000"/>
@@ -312,11 +312,6 @@
     <font>
       <color rgb="FF000000"/>
       <name val="Arial"/>
-    </font>
-    <font>
-      <color theme="1"/>
-      <name val="Arial"/>
-      <scheme val="minor"/>
     </font>
     <font>
       <color rgb="FF000000"/>
@@ -390,7 +385,7 @@
     <xf borderId="0" fillId="0" fontId="5" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
       <alignment vertical="bottom"/>
     </xf>
-    <xf borderId="0" fillId="0" fontId="6" numFmtId="0" xfId="0" applyFont="1"/>
+    <xf borderId="0" fillId="0" fontId="4" numFmtId="0" xfId="0" applyFont="1"/>
     <xf borderId="0" fillId="0" fontId="5" numFmtId="11" xfId="0" applyAlignment="1" applyFont="1" applyNumberFormat="1">
       <alignment vertical="top"/>
     </xf>
@@ -406,14 +401,14 @@
     <xf borderId="0" fillId="2" fontId="5" numFmtId="11" xfId="0" applyAlignment="1" applyFont="1" applyNumberFormat="1">
       <alignment shrinkToFit="0" vertical="bottom" wrapText="0"/>
     </xf>
-    <xf borderId="0" fillId="2" fontId="7" numFmtId="0" xfId="0" applyFont="1"/>
+    <xf borderId="0" fillId="2" fontId="6" numFmtId="0" xfId="0" applyFont="1"/>
     <xf borderId="0" fillId="0" fontId="4" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
       <alignment shrinkToFit="0" vertical="bottom" wrapText="0"/>
     </xf>
     <xf borderId="0" fillId="0" fontId="5" numFmtId="11" xfId="0" applyAlignment="1" applyFont="1" applyNumberFormat="1">
       <alignment horizontal="right" shrinkToFit="0" vertical="top" wrapText="1"/>
     </xf>
-    <xf borderId="0" fillId="2" fontId="7" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
+    <xf borderId="0" fillId="2" fontId="6" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
       <alignment vertical="bottom"/>
     </xf>
     <xf borderId="0" fillId="0" fontId="4" numFmtId="11" xfId="0" applyAlignment="1" applyFont="1" applyNumberFormat="1">
@@ -2116,7 +2111,7 @@
       <c r="Y20" s="8"/>
       <c r="Z20" s="8"/>
     </row>
-    <row r="21">
+    <row r="21" ht="15.75" customHeight="1">
       <c r="A21" s="8"/>
       <c r="B21" s="8" t="s">
         <v>19</v>
@@ -2148,7 +2143,7 @@
       <c r="Y21" s="8"/>
       <c r="Z21" s="8"/>
     </row>
-    <row r="22">
+    <row r="22" ht="15.75" customHeight="1">
       <c r="A22" s="8"/>
       <c r="B22" s="8" t="s">
         <v>20</v>
@@ -2180,7 +2175,7 @@
       <c r="Y22" s="8"/>
       <c r="Z22" s="8"/>
     </row>
-    <row r="23">
+    <row r="23" ht="15.75" customHeight="1">
       <c r="A23" s="8"/>
       <c r="B23" s="8" t="s">
         <v>22</v>
@@ -2212,7 +2207,7 @@
       <c r="Y23" s="8"/>
       <c r="Z23" s="8"/>
     </row>
-    <row r="24">
+    <row r="24" ht="15.75" customHeight="1">
       <c r="A24" s="8"/>
       <c r="B24" s="8" t="s">
         <v>23</v>
@@ -2244,7 +2239,7 @@
       <c r="Y24" s="8"/>
       <c r="Z24" s="8"/>
     </row>
-    <row r="25">
+    <row r="25" ht="15.75" customHeight="1">
       <c r="A25" s="8"/>
       <c r="B25" s="8" t="s">
         <v>25</v>
@@ -2276,7 +2271,7 @@
       <c r="Y25" s="8"/>
       <c r="Z25" s="8"/>
     </row>
-    <row r="26">
+    <row r="26" ht="15.75" customHeight="1">
       <c r="A26" s="8"/>
       <c r="B26" s="9" t="s">
         <v>26</v>
@@ -2308,7 +2303,7 @@
       <c r="Y26" s="8"/>
       <c r="Z26" s="8"/>
     </row>
-    <row r="27">
+    <row r="27" ht="15.75" customHeight="1">
       <c r="A27" s="8"/>
       <c r="B27" s="8" t="s">
         <v>28</v>
@@ -2340,7 +2335,7 @@
       <c r="Y27" s="8"/>
       <c r="Z27" s="8"/>
     </row>
-    <row r="28">
+    <row r="28" ht="15.75" customHeight="1">
       <c r="A28" s="8"/>
       <c r="B28" s="15" t="s">
         <v>30</v>
@@ -2372,7 +2367,7 @@
       <c r="Y28" s="8"/>
       <c r="Z28" s="8"/>
     </row>
-    <row r="29">
+    <row r="29" ht="15.75" customHeight="1">
       <c r="A29" s="8"/>
       <c r="B29" s="8"/>
       <c r="C29" s="6"/>
@@ -2380,7 +2375,7 @@
       <c r="E29" s="8"/>
       <c r="F29" s="8"/>
     </row>
-    <row r="30">
+    <row r="30" ht="15.75" customHeight="1">
       <c r="A30" s="7" t="s">
         <v>35</v>
       </c>
@@ -2390,7 +2385,7 @@
       <c r="E30" s="8"/>
       <c r="F30" s="8"/>
     </row>
-    <row r="31">
+    <row r="31" ht="15.75" customHeight="1">
       <c r="A31" s="8"/>
       <c r="B31" s="8" t="s">
         <v>10</v>
@@ -2402,7 +2397,7 @@
       <c r="E31" s="8"/>
       <c r="F31" s="8"/>
     </row>
-    <row r="32">
+    <row r="32" ht="15.75" customHeight="1">
       <c r="A32" s="8"/>
       <c r="B32" s="8" t="s">
         <v>12</v>
@@ -2414,7 +2409,7 @@
       <c r="E32" s="8"/>
       <c r="F32" s="8"/>
     </row>
-    <row r="33">
+    <row r="33" ht="15.75" customHeight="1">
       <c r="A33" s="9"/>
       <c r="B33" s="9" t="s">
         <v>2</v>
@@ -2426,7 +2421,7 @@
       <c r="E33" s="6"/>
       <c r="F33" s="6"/>
     </row>
-    <row r="34">
+    <row r="34" ht="15.75" customHeight="1">
       <c r="A34" s="8"/>
       <c r="B34" s="8" t="s">
         <v>19</v>
@@ -2438,7 +2433,7 @@
       <c r="E34" s="8"/>
       <c r="F34" s="8"/>
     </row>
-    <row r="35">
+    <row r="35" ht="15.75" customHeight="1">
       <c r="A35" s="8"/>
       <c r="B35" s="8" t="s">
         <v>20</v>
@@ -2450,7 +2445,7 @@
       <c r="E35" s="8"/>
       <c r="F35" s="8"/>
     </row>
-    <row r="36">
+    <row r="36" ht="15.75" customHeight="1">
       <c r="A36" s="8"/>
       <c r="B36" s="8" t="s">
         <v>22</v>
@@ -2462,7 +2457,7 @@
       <c r="E36" s="8"/>
       <c r="F36" s="8"/>
     </row>
-    <row r="37">
+    <row r="37" ht="15.75" customHeight="1">
       <c r="A37" s="8"/>
       <c r="B37" s="8" t="s">
         <v>23</v>
@@ -2474,7 +2469,7 @@
       <c r="E37" s="8"/>
       <c r="F37" s="8"/>
     </row>
-    <row r="38">
+    <row r="38" ht="15.75" customHeight="1">
       <c r="A38" s="8"/>
       <c r="B38" s="8" t="s">
         <v>25</v>
@@ -2486,7 +2481,7 @@
       <c r="E38" s="8"/>
       <c r="F38" s="8"/>
     </row>
-    <row r="39">
+    <row r="39" ht="15.75" customHeight="1">
       <c r="A39" s="8"/>
       <c r="B39" s="9" t="s">
         <v>26</v>
@@ -2498,7 +2493,7 @@
       </c>
       <c r="F39" s="8"/>
     </row>
-    <row r="40">
+    <row r="40" ht="15.75" customHeight="1">
       <c r="A40" s="8"/>
       <c r="B40" s="8" t="s">
         <v>28</v>
@@ -2510,7 +2505,7 @@
       <c r="E40" s="8"/>
       <c r="F40" s="8"/>
     </row>
-    <row r="41">
+    <row r="41" ht="15.75" customHeight="1">
       <c r="A41" s="8"/>
       <c r="B41" s="15" t="s">
         <v>30</v>
@@ -2522,7 +2517,7 @@
       <c r="E41" s="8"/>
       <c r="F41" s="8"/>
     </row>
-    <row r="42">
+    <row r="42" ht="15.75" customHeight="1">
       <c r="A42" s="8"/>
       <c r="B42" s="8"/>
       <c r="C42" s="8"/>
@@ -2530,7 +2525,7 @@
       <c r="E42" s="8"/>
       <c r="F42" s="8"/>
     </row>
-    <row r="43">
+    <row r="43" ht="15.75" customHeight="1">
       <c r="A43" s="7" t="s">
         <v>38</v>
       </c>
@@ -2540,7 +2535,7 @@
       <c r="E43" s="8"/>
       <c r="F43" s="8"/>
     </row>
-    <row r="44">
+    <row r="44" ht="15.75" customHeight="1">
       <c r="A44" s="8"/>
       <c r="B44" s="8" t="s">
         <v>10</v>
@@ -2552,7 +2547,7 @@
       <c r="E44" s="8"/>
       <c r="F44" s="8"/>
     </row>
-    <row r="45">
+    <row r="45" ht="15.75" customHeight="1">
       <c r="A45" s="8"/>
       <c r="B45" s="8" t="s">
         <v>12</v>
@@ -2564,7 +2559,7 @@
       <c r="E45" s="8"/>
       <c r="F45" s="8"/>
     </row>
-    <row r="46">
+    <row r="46" ht="15.75" customHeight="1">
       <c r="A46" s="9"/>
       <c r="B46" s="9" t="s">
         <v>2</v>
@@ -2576,7 +2571,7 @@
       <c r="E46" s="6"/>
       <c r="F46" s="8"/>
     </row>
-    <row r="47">
+    <row r="47" ht="15.75" customHeight="1">
       <c r="A47" s="8"/>
       <c r="B47" s="8" t="s">
         <v>19</v>
@@ -2588,7 +2583,7 @@
       <c r="E47" s="8"/>
       <c r="F47" s="8"/>
     </row>
-    <row r="48">
+    <row r="48" ht="15.75" customHeight="1">
       <c r="A48" s="8"/>
       <c r="B48" s="8" t="s">
         <v>20</v>
@@ -2600,7 +2595,7 @@
       <c r="E48" s="8"/>
       <c r="F48" s="8"/>
     </row>
-    <row r="49">
+    <row r="49" ht="15.75" customHeight="1">
       <c r="A49" s="8"/>
       <c r="B49" s="8" t="s">
         <v>22</v>
@@ -2612,7 +2607,7 @@
       <c r="E49" s="8"/>
       <c r="F49" s="8"/>
     </row>
-    <row r="50">
+    <row r="50" ht="15.75" customHeight="1">
       <c r="A50" s="8"/>
       <c r="B50" s="8" t="s">
         <v>23</v>
@@ -2624,7 +2619,7 @@
       <c r="E50" s="8"/>
       <c r="F50" s="8"/>
     </row>
-    <row r="51">
+    <row r="51" ht="15.75" customHeight="1">
       <c r="A51" s="8"/>
       <c r="B51" s="8" t="s">
         <v>25</v>
@@ -2636,7 +2631,7 @@
       <c r="E51" s="8"/>
       <c r="F51" s="8"/>
     </row>
-    <row r="52">
+    <row r="52" ht="15.75" customHeight="1">
       <c r="A52" s="8"/>
       <c r="B52" s="9" t="s">
         <v>26</v>
@@ -2648,7 +2643,7 @@
       </c>
       <c r="F52" s="8"/>
     </row>
-    <row r="53">
+    <row r="53" ht="15.75" customHeight="1">
       <c r="A53" s="8"/>
       <c r="B53" s="8" t="s">
         <v>28</v>
@@ -2660,7 +2655,7 @@
       <c r="E53" s="8"/>
       <c r="F53" s="8"/>
     </row>
-    <row r="54">
+    <row r="54" ht="15.75" customHeight="1">
       <c r="A54" s="8"/>
       <c r="B54" s="15" t="s">
         <v>30</v>
@@ -2672,7 +2667,7 @@
       <c r="E54" s="8"/>
       <c r="F54" s="8"/>
     </row>
-    <row r="55">
+    <row r="55" ht="15.75" customHeight="1">
       <c r="A55" s="7"/>
       <c r="B55" s="8"/>
       <c r="C55" s="8"/>
@@ -2680,12 +2675,12 @@
       <c r="E55" s="8"/>
       <c r="F55" s="8"/>
     </row>
-    <row r="56">
+    <row r="56" ht="15.75" customHeight="1">
       <c r="A56" s="2"/>
       <c r="B56" s="2"/>
       <c r="C56" s="19"/>
     </row>
-    <row r="57">
+    <row r="57" ht="15.75" customHeight="1">
       <c r="A57" s="7" t="s">
         <v>41</v>
       </c>
@@ -2695,7 +2690,7 @@
       <c r="E57" s="8"/>
       <c r="F57" s="8"/>
     </row>
-    <row r="58">
+    <row r="58" ht="15.75" customHeight="1">
       <c r="A58" s="8"/>
       <c r="B58" s="8" t="s">
         <v>10</v>
@@ -2707,7 +2702,7 @@
       <c r="E58" s="8"/>
       <c r="F58" s="8"/>
     </row>
-    <row r="59">
+    <row r="59" ht="15.75" customHeight="1">
       <c r="A59" s="8"/>
       <c r="B59" s="8" t="s">
         <v>12</v>
@@ -2719,7 +2714,7 @@
       <c r="E59" s="8"/>
       <c r="F59" s="8"/>
     </row>
-    <row r="60">
+    <row r="60" ht="15.75" customHeight="1">
       <c r="A60" s="9"/>
       <c r="B60" s="9" t="s">
         <v>2</v>
@@ -2733,7 +2728,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="61">
+    <row r="61" ht="15.75" customHeight="1">
       <c r="A61" s="8"/>
       <c r="B61" s="9" t="s">
         <v>16</v>
@@ -2747,7 +2742,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="62">
+    <row r="62" ht="15.75" customHeight="1">
       <c r="A62" s="8"/>
       <c r="B62" s="8" t="s">
         <v>19</v>
@@ -2759,7 +2754,7 @@
       <c r="E62" s="8"/>
       <c r="F62" s="8"/>
     </row>
-    <row r="63">
+    <row r="63" ht="15.75" customHeight="1">
       <c r="A63" s="8"/>
       <c r="B63" s="8" t="s">
         <v>20</v>
@@ -2771,7 +2766,7 @@
       <c r="E63" s="8"/>
       <c r="F63" s="8"/>
     </row>
-    <row r="64">
+    <row r="64" ht="15.75" customHeight="1">
       <c r="A64" s="8"/>
       <c r="B64" s="8" t="s">
         <v>22</v>
@@ -2783,7 +2778,7 @@
       <c r="E64" s="8"/>
       <c r="F64" s="8"/>
     </row>
-    <row r="65">
+    <row r="65" ht="15.75" customHeight="1">
       <c r="A65" s="8"/>
       <c r="B65" s="8" t="s">
         <v>23</v>
@@ -2795,7 +2790,7 @@
       <c r="E65" s="8"/>
       <c r="F65" s="8"/>
     </row>
-    <row r="66">
+    <row r="66" ht="15.75" customHeight="1">
       <c r="A66" s="8"/>
       <c r="B66" s="8" t="s">
         <v>25</v>
@@ -2807,7 +2802,7 @@
       <c r="E66" s="8"/>
       <c r="F66" s="8"/>
     </row>
-    <row r="67">
+    <row r="67" ht="15.75" customHeight="1">
       <c r="A67" s="8"/>
       <c r="B67" s="9" t="s">
         <v>26</v>
@@ -2819,7 +2814,7 @@
       </c>
       <c r="F67" s="8"/>
     </row>
-    <row r="68">
+    <row r="68" ht="15.75" customHeight="1">
       <c r="A68" s="8"/>
       <c r="B68" s="8" t="s">
         <v>28</v>
@@ -2831,7 +2826,7 @@
       <c r="E68" s="8"/>
       <c r="F68" s="8"/>
     </row>
-    <row r="69">
+    <row r="69" ht="15.75" customHeight="1">
       <c r="A69" s="8"/>
       <c r="B69" s="15" t="s">
         <v>30</v>
@@ -2843,12 +2838,12 @@
       <c r="E69" s="8"/>
       <c r="F69" s="8"/>
     </row>
-    <row r="70">
+    <row r="70" ht="15.75" customHeight="1">
       <c r="A70" s="16"/>
       <c r="B70" s="2"/>
       <c r="C70" s="2"/>
     </row>
-    <row r="71">
+    <row r="71" ht="15.75" customHeight="1">
       <c r="A71" s="7" t="s">
         <v>44</v>
       </c>
@@ -2858,7 +2853,7 @@
       <c r="E71" s="8"/>
       <c r="F71" s="8"/>
     </row>
-    <row r="72">
+    <row r="72" ht="15.75" customHeight="1">
       <c r="A72" s="8"/>
       <c r="B72" s="8" t="s">
         <v>10</v>
@@ -2870,7 +2865,7 @@
       <c r="E72" s="8"/>
       <c r="F72" s="8"/>
     </row>
-    <row r="73">
+    <row r="73" ht="15.75" customHeight="1">
       <c r="A73" s="8"/>
       <c r="B73" s="8" t="s">
         <v>12</v>
@@ -2882,7 +2877,7 @@
       <c r="E73" s="8"/>
       <c r="F73" s="8"/>
     </row>
-    <row r="74">
+    <row r="74" ht="15.75" customHeight="1">
       <c r="A74" s="9"/>
       <c r="B74" s="9" t="s">
         <v>2</v>
@@ -2896,7 +2891,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="75">
+    <row r="75" ht="15.75" customHeight="1">
       <c r="A75" s="8"/>
       <c r="B75" s="9" t="s">
         <v>16</v>
@@ -2910,7 +2905,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="76">
+    <row r="76" ht="15.75" customHeight="1">
       <c r="A76" s="8"/>
       <c r="B76" s="8" t="s">
         <v>19</v>
@@ -2922,7 +2917,7 @@
       <c r="E76" s="8"/>
       <c r="F76" s="8"/>
     </row>
-    <row r="77">
+    <row r="77" ht="15.75" customHeight="1">
       <c r="A77" s="8"/>
       <c r="B77" s="8" t="s">
         <v>20</v>
@@ -2934,7 +2929,7 @@
       <c r="E77" s="8"/>
       <c r="F77" s="8"/>
     </row>
-    <row r="78">
+    <row r="78" ht="15.75" customHeight="1">
       <c r="A78" s="8"/>
       <c r="B78" s="8" t="s">
         <v>22</v>
@@ -2946,7 +2941,7 @@
       <c r="E78" s="8"/>
       <c r="F78" s="8"/>
     </row>
-    <row r="79">
+    <row r="79" ht="15.75" customHeight="1">
       <c r="A79" s="8"/>
       <c r="B79" s="8" t="s">
         <v>23</v>
@@ -2958,7 +2953,7 @@
       <c r="E79" s="8"/>
       <c r="F79" s="8"/>
     </row>
-    <row r="80">
+    <row r="80" ht="15.75" customHeight="1">
       <c r="A80" s="8"/>
       <c r="B80" s="8" t="s">
         <v>25</v>
@@ -2970,7 +2965,7 @@
       <c r="E80" s="8"/>
       <c r="F80" s="8"/>
     </row>
-    <row r="81">
+    <row r="81" ht="15.75" customHeight="1">
       <c r="A81" s="8"/>
       <c r="B81" s="9" t="s">
         <v>26</v>
@@ -2982,7 +2977,7 @@
       </c>
       <c r="F81" s="8"/>
     </row>
-    <row r="82">
+    <row r="82" ht="15.75" customHeight="1">
       <c r="A82" s="8"/>
       <c r="B82" s="8" t="s">
         <v>28</v>
@@ -2994,7 +2989,7 @@
       <c r="E82" s="8"/>
       <c r="F82" s="8"/>
     </row>
-    <row r="83">
+    <row r="83" ht="15.75" customHeight="1">
       <c r="A83" s="8"/>
       <c r="B83" s="15" t="s">
         <v>30</v>
@@ -3006,7 +3001,7 @@
       <c r="E83" s="8"/>
       <c r="F83" s="8"/>
     </row>
-    <row r="84">
+    <row r="84" ht="15.75" customHeight="1">
       <c r="A84" s="8"/>
       <c r="B84" s="8"/>
       <c r="C84" s="6"/>
@@ -3014,7 +3009,7 @@
       <c r="E84" s="8"/>
       <c r="F84" s="8"/>
     </row>
-    <row r="85">
+    <row r="85" ht="15.75" customHeight="1">
       <c r="A85" s="7" t="s">
         <v>46</v>
       </c>
@@ -3024,7 +3019,7 @@
       <c r="E85" s="8"/>
       <c r="F85" s="8"/>
     </row>
-    <row r="86">
+    <row r="86" ht="15.75" customHeight="1">
       <c r="A86" s="8"/>
       <c r="B86" s="8" t="s">
         <v>10</v>
@@ -3036,7 +3031,7 @@
       <c r="E86" s="8"/>
       <c r="F86" s="8"/>
     </row>
-    <row r="87">
+    <row r="87" ht="15.75" customHeight="1">
       <c r="A87" s="8"/>
       <c r="B87" s="8" t="s">
         <v>12</v>
@@ -3048,7 +3043,7 @@
       <c r="E87" s="8"/>
       <c r="F87" s="8"/>
     </row>
-    <row r="88">
+    <row r="88" ht="15.75" customHeight="1">
       <c r="A88" s="9"/>
       <c r="B88" s="9" t="s">
         <v>2</v>
@@ -3060,7 +3055,7 @@
       <c r="E88" s="6"/>
       <c r="F88" s="6"/>
     </row>
-    <row r="89">
+    <row r="89" ht="15.75" customHeight="1">
       <c r="A89" s="8"/>
       <c r="B89" s="8" t="s">
         <v>19</v>
@@ -3072,7 +3067,7 @@
       <c r="E89" s="8"/>
       <c r="F89" s="8"/>
     </row>
-    <row r="90">
+    <row r="90" ht="15.75" customHeight="1">
       <c r="A90" s="8"/>
       <c r="B90" s="8" t="s">
         <v>20</v>
@@ -3084,7 +3079,7 @@
       <c r="E90" s="8"/>
       <c r="F90" s="8"/>
     </row>
-    <row r="91">
+    <row r="91" ht="15.75" customHeight="1">
       <c r="A91" s="8"/>
       <c r="B91" s="8" t="s">
         <v>22</v>
@@ -3096,7 +3091,7 @@
       <c r="E91" s="8"/>
       <c r="F91" s="8"/>
     </row>
-    <row r="92">
+    <row r="92" ht="15.75" customHeight="1">
       <c r="A92" s="8"/>
       <c r="B92" s="8" t="s">
         <v>23</v>
@@ -3108,7 +3103,7 @@
       <c r="E92" s="8"/>
       <c r="F92" s="8"/>
     </row>
-    <row r="93">
+    <row r="93" ht="15.75" customHeight="1">
       <c r="A93" s="8"/>
       <c r="B93" s="8" t="s">
         <v>25</v>
@@ -3120,7 +3115,7 @@
       <c r="E93" s="8"/>
       <c r="F93" s="8"/>
     </row>
-    <row r="94">
+    <row r="94" ht="15.75" customHeight="1">
       <c r="A94" s="8"/>
       <c r="B94" s="9" t="s">
         <v>26</v>
@@ -3132,7 +3127,7 @@
       </c>
       <c r="F94" s="8"/>
     </row>
-    <row r="95">
+    <row r="95" ht="15.75" customHeight="1">
       <c r="A95" s="8"/>
       <c r="B95" s="8" t="s">
         <v>28</v>
@@ -3144,7 +3139,7 @@
       <c r="E95" s="8"/>
       <c r="F95" s="8"/>
     </row>
-    <row r="96">
+    <row r="96" ht="15.75" customHeight="1">
       <c r="A96" s="8"/>
       <c r="B96" s="15" t="s">
         <v>30</v>
@@ -3156,10 +3151,10 @@
       <c r="E96" s="8"/>
       <c r="F96" s="8"/>
     </row>
-    <row r="97">
+    <row r="97" ht="15.75" customHeight="1">
       <c r="C97" s="20"/>
     </row>
-    <row r="98">
+    <row r="98" ht="15.75" customHeight="1">
       <c r="A98" s="7" t="s">
         <v>48</v>
       </c>
@@ -3169,7 +3164,7 @@
       <c r="E98" s="8"/>
       <c r="F98" s="8"/>
     </row>
-    <row r="99">
+    <row r="99" ht="15.75" customHeight="1">
       <c r="A99" s="8"/>
       <c r="B99" s="8" t="s">
         <v>10</v>
@@ -3181,7 +3176,7 @@
       <c r="E99" s="8"/>
       <c r="F99" s="8"/>
     </row>
-    <row r="100">
+    <row r="100" ht="15.75" customHeight="1">
       <c r="A100" s="8"/>
       <c r="B100" s="8" t="s">
         <v>12</v>
@@ -3193,7 +3188,7 @@
       <c r="E100" s="8"/>
       <c r="F100" s="8"/>
     </row>
-    <row r="101">
+    <row r="101" ht="15.75" customHeight="1">
       <c r="A101" s="9"/>
       <c r="B101" s="9" t="s">
         <v>2</v>
@@ -3205,7 +3200,7 @@
       <c r="E101" s="6"/>
       <c r="F101" s="8"/>
     </row>
-    <row r="102">
+    <row r="102" ht="15.75" customHeight="1">
       <c r="A102" s="8"/>
       <c r="B102" s="8" t="s">
         <v>19</v>
@@ -3217,7 +3212,7 @@
       <c r="E102" s="8"/>
       <c r="F102" s="8"/>
     </row>
-    <row r="103">
+    <row r="103" ht="15.75" customHeight="1">
       <c r="A103" s="8"/>
       <c r="B103" s="8" t="s">
         <v>20</v>
@@ -3229,7 +3224,7 @@
       <c r="E103" s="8"/>
       <c r="F103" s="8"/>
     </row>
-    <row r="104">
+    <row r="104" ht="15.75" customHeight="1">
       <c r="A104" s="8"/>
       <c r="B104" s="8" t="s">
         <v>22</v>
@@ -3241,7 +3236,7 @@
       <c r="E104" s="8"/>
       <c r="F104" s="8"/>
     </row>
-    <row r="105">
+    <row r="105" ht="15.75" customHeight="1">
       <c r="A105" s="8"/>
       <c r="B105" s="8" t="s">
         <v>23</v>
@@ -3253,7 +3248,7 @@
       <c r="E105" s="8"/>
       <c r="F105" s="8"/>
     </row>
-    <row r="106">
+    <row r="106" ht="15.75" customHeight="1">
       <c r="A106" s="8"/>
       <c r="B106" s="8" t="s">
         <v>25</v>
@@ -3265,7 +3260,7 @@
       <c r="E106" s="8"/>
       <c r="F106" s="8"/>
     </row>
-    <row r="107">
+    <row r="107" ht="15.75" customHeight="1">
       <c r="A107" s="8"/>
       <c r="B107" s="9" t="s">
         <v>26</v>
@@ -3277,7 +3272,7 @@
       </c>
       <c r="F107" s="8"/>
     </row>
-    <row r="108">
+    <row r="108" ht="15.75" customHeight="1">
       <c r="A108" s="8"/>
       <c r="B108" s="8" t="s">
         <v>28</v>
@@ -3289,7 +3284,7 @@
       <c r="E108" s="8"/>
       <c r="F108" s="8"/>
     </row>
-    <row r="109">
+    <row r="109" ht="15.75" customHeight="1">
       <c r="A109" s="8"/>
       <c r="B109" s="15" t="s">
         <v>30</v>
@@ -3301,10 +3296,10 @@
       <c r="E109" s="8"/>
       <c r="F109" s="8"/>
     </row>
-    <row r="110">
+    <row r="110" ht="15.75" customHeight="1">
       <c r="C110" s="20"/>
     </row>
-    <row r="111">
+    <row r="111" ht="15.75" customHeight="1">
       <c r="A111" s="7" t="s">
         <v>50</v>
       </c>
@@ -3314,7 +3309,7 @@
       <c r="E111" s="8"/>
       <c r="F111" s="8"/>
     </row>
-    <row r="112">
+    <row r="112" ht="15.75" customHeight="1">
       <c r="A112" s="8"/>
       <c r="B112" s="8" t="s">
         <v>10</v>
@@ -3326,7 +3321,7 @@
       <c r="E112" s="8"/>
       <c r="F112" s="8"/>
     </row>
-    <row r="113">
+    <row r="113" ht="15.75" customHeight="1">
       <c r="A113" s="8"/>
       <c r="B113" s="8" t="s">
         <v>12</v>
@@ -3338,7 +3333,7 @@
       <c r="E113" s="8"/>
       <c r="F113" s="8"/>
     </row>
-    <row r="114">
+    <row r="114" ht="15.75" customHeight="1">
       <c r="A114" s="9"/>
       <c r="B114" s="9" t="s">
         <v>2</v>
@@ -3352,7 +3347,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="115">
+    <row r="115" ht="15.75" customHeight="1">
       <c r="A115" s="8"/>
       <c r="B115" s="9" t="s">
         <v>16</v>
@@ -3366,7 +3361,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="116">
+    <row r="116" ht="15.75" customHeight="1">
       <c r="A116" s="8"/>
       <c r="B116" s="8" t="s">
         <v>19</v>
@@ -3378,7 +3373,7 @@
       <c r="E116" s="8"/>
       <c r="F116" s="8"/>
     </row>
-    <row r="117">
+    <row r="117" ht="15.75" customHeight="1">
       <c r="A117" s="8"/>
       <c r="B117" s="8" t="s">
         <v>20</v>
@@ -3390,7 +3385,7 @@
       <c r="E117" s="8"/>
       <c r="F117" s="8"/>
     </row>
-    <row r="118">
+    <row r="118" ht="15.75" customHeight="1">
       <c r="A118" s="8"/>
       <c r="B118" s="8" t="s">
         <v>22</v>
@@ -3402,7 +3397,7 @@
       <c r="E118" s="8"/>
       <c r="F118" s="8"/>
     </row>
-    <row r="119">
+    <row r="119" ht="15.75" customHeight="1">
       <c r="A119" s="8"/>
       <c r="B119" s="8" t="s">
         <v>23</v>
@@ -3414,7 +3409,7 @@
       <c r="E119" s="8"/>
       <c r="F119" s="8"/>
     </row>
-    <row r="120">
+    <row r="120" ht="15.75" customHeight="1">
       <c r="A120" s="8"/>
       <c r="B120" s="8" t="s">
         <v>25</v>
@@ -3426,7 +3421,7 @@
       <c r="E120" s="8"/>
       <c r="F120" s="8"/>
     </row>
-    <row r="121">
+    <row r="121" ht="15.75" customHeight="1">
       <c r="A121" s="8"/>
       <c r="B121" s="9" t="s">
         <v>26</v>
@@ -3438,7 +3433,7 @@
       </c>
       <c r="F121" s="8"/>
     </row>
-    <row r="122">
+    <row r="122" ht="15.75" customHeight="1">
       <c r="A122" s="8"/>
       <c r="B122" s="8" t="s">
         <v>28</v>
@@ -3450,7 +3445,7 @@
       <c r="E122" s="8"/>
       <c r="F122" s="8"/>
     </row>
-    <row r="123">
+    <row r="123" ht="15.75" customHeight="1">
       <c r="A123" s="8"/>
       <c r="B123" s="15" t="s">
         <v>30</v>
@@ -3462,12 +3457,12 @@
       <c r="E123" s="8"/>
       <c r="F123" s="8"/>
     </row>
-    <row r="124">
+    <row r="124" ht="15.75" customHeight="1">
       <c r="A124" s="16"/>
       <c r="B124" s="2"/>
       <c r="C124" s="2"/>
     </row>
-    <row r="125">
+    <row r="125" ht="15.75" customHeight="1">
       <c r="A125" s="7" t="s">
         <v>53</v>
       </c>
@@ -3477,7 +3472,7 @@
       <c r="E125" s="8"/>
       <c r="F125" s="8"/>
     </row>
-    <row r="126">
+    <row r="126" ht="15.75" customHeight="1">
       <c r="A126" s="8"/>
       <c r="B126" s="8" t="s">
         <v>10</v>
@@ -3489,7 +3484,7 @@
       <c r="E126" s="8"/>
       <c r="F126" s="8"/>
     </row>
-    <row r="127">
+    <row r="127" ht="15.75" customHeight="1">
       <c r="A127" s="8"/>
       <c r="B127" s="8" t="s">
         <v>12</v>
@@ -3501,7 +3496,7 @@
       <c r="E127" s="8"/>
       <c r="F127" s="8"/>
     </row>
-    <row r="128">
+    <row r="128" ht="15.75" customHeight="1">
       <c r="A128" s="9"/>
       <c r="B128" s="9" t="s">
         <v>2</v>
@@ -3515,7 +3510,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="129">
+    <row r="129" ht="15.75" customHeight="1">
       <c r="A129" s="8"/>
       <c r="B129" s="9" t="s">
         <v>16</v>
@@ -3529,7 +3524,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="130">
+    <row r="130" ht="15.75" customHeight="1">
       <c r="A130" s="8"/>
       <c r="B130" s="8" t="s">
         <v>19</v>
@@ -3541,7 +3536,7 @@
       </c>
       <c r="F130" s="8"/>
     </row>
-    <row r="131">
+    <row r="131" ht="15.75" customHeight="1">
       <c r="A131" s="8"/>
       <c r="B131" s="8" t="s">
         <v>20</v>
@@ -3553,7 +3548,7 @@
       <c r="E131" s="8"/>
       <c r="F131" s="8"/>
     </row>
-    <row r="132">
+    <row r="132" ht="15.75" customHeight="1">
       <c r="A132" s="8"/>
       <c r="B132" s="8" t="s">
         <v>22</v>
@@ -3565,7 +3560,7 @@
       <c r="E132" s="8"/>
       <c r="F132" s="8"/>
     </row>
-    <row r="133">
+    <row r="133" ht="15.75" customHeight="1">
       <c r="A133" s="8"/>
       <c r="B133" s="8" t="s">
         <v>23</v>
@@ -3577,7 +3572,7 @@
       <c r="E133" s="8"/>
       <c r="F133" s="8"/>
     </row>
-    <row r="134">
+    <row r="134" ht="15.75" customHeight="1">
       <c r="A134" s="8"/>
       <c r="B134" s="8" t="s">
         <v>25</v>
@@ -3589,7 +3584,7 @@
       <c r="E134" s="8"/>
       <c r="F134" s="8"/>
     </row>
-    <row r="135">
+    <row r="135" ht="15.75" customHeight="1">
       <c r="A135" s="8"/>
       <c r="B135" s="9" t="s">
         <v>26</v>
@@ -3601,7 +3596,7 @@
       </c>
       <c r="F135" s="8"/>
     </row>
-    <row r="136">
+    <row r="136" ht="15.75" customHeight="1">
       <c r="A136" s="8"/>
       <c r="B136" s="8" t="s">
         <v>28</v>
@@ -3613,7 +3608,7 @@
       <c r="E136" s="8"/>
       <c r="F136" s="8"/>
     </row>
-    <row r="137">
+    <row r="137" ht="15.75" customHeight="1">
       <c r="A137" s="8"/>
       <c r="B137" s="15" t="s">
         <v>30</v>
@@ -3625,7 +3620,7 @@
       <c r="E137" s="8"/>
       <c r="F137" s="8"/>
     </row>
-    <row r="138">
+    <row r="138" ht="15.75" customHeight="1">
       <c r="A138" s="8"/>
       <c r="B138" s="8"/>
       <c r="C138" s="6"/>
@@ -3633,7 +3628,7 @@
       <c r="E138" s="8"/>
       <c r="F138" s="8"/>
     </row>
-    <row r="139">
+    <row r="139" ht="15.75" customHeight="1">
       <c r="A139" s="7" t="s">
         <v>55</v>
       </c>
@@ -3643,7 +3638,7 @@
       <c r="E139" s="8"/>
       <c r="F139" s="8"/>
     </row>
-    <row r="140">
+    <row r="140" ht="15.75" customHeight="1">
       <c r="A140" s="8"/>
       <c r="B140" s="8" t="s">
         <v>10</v>
@@ -3655,7 +3650,7 @@
       <c r="E140" s="8"/>
       <c r="F140" s="8"/>
     </row>
-    <row r="141">
+    <row r="141" ht="15.75" customHeight="1">
       <c r="A141" s="8"/>
       <c r="B141" s="8" t="s">
         <v>12</v>
@@ -3667,7 +3662,7 @@
       <c r="E141" s="8"/>
       <c r="F141" s="8"/>
     </row>
-    <row r="142">
+    <row r="142" ht="15.75" customHeight="1">
       <c r="A142" s="9"/>
       <c r="B142" s="9" t="s">
         <v>2</v>
@@ -3679,7 +3674,7 @@
       <c r="E142" s="6"/>
       <c r="F142" s="6"/>
     </row>
-    <row r="143">
+    <row r="143" ht="15.75" customHeight="1">
       <c r="A143" s="8"/>
       <c r="B143" s="8" t="s">
         <v>19</v>
@@ -3691,7 +3686,7 @@
       <c r="E143" s="8"/>
       <c r="F143" s="8"/>
     </row>
-    <row r="144">
+    <row r="144" ht="15.75" customHeight="1">
       <c r="A144" s="8"/>
       <c r="B144" s="8" t="s">
         <v>20</v>
@@ -3703,7 +3698,7 @@
       <c r="E144" s="8"/>
       <c r="F144" s="8"/>
     </row>
-    <row r="145">
+    <row r="145" ht="15.75" customHeight="1">
       <c r="A145" s="8"/>
       <c r="B145" s="8" t="s">
         <v>22</v>
@@ -3715,7 +3710,7 @@
       <c r="E145" s="8"/>
       <c r="F145" s="8"/>
     </row>
-    <row r="146">
+    <row r="146" ht="15.75" customHeight="1">
       <c r="A146" s="8"/>
       <c r="B146" s="8" t="s">
         <v>23</v>
@@ -3727,7 +3722,7 @@
       <c r="E146" s="8"/>
       <c r="F146" s="8"/>
     </row>
-    <row r="147">
+    <row r="147" ht="15.75" customHeight="1">
       <c r="A147" s="8"/>
       <c r="B147" s="8" t="s">
         <v>25</v>
@@ -3739,7 +3734,7 @@
       <c r="E147" s="8"/>
       <c r="F147" s="8"/>
     </row>
-    <row r="148">
+    <row r="148" ht="15.75" customHeight="1">
       <c r="A148" s="8"/>
       <c r="B148" s="9" t="s">
         <v>26</v>
@@ -3751,7 +3746,7 @@
       </c>
       <c r="F148" s="8"/>
     </row>
-    <row r="149">
+    <row r="149" ht="15.75" customHeight="1">
       <c r="A149" s="8"/>
       <c r="B149" s="8" t="s">
         <v>28</v>
@@ -3763,7 +3758,7 @@
       <c r="E149" s="8"/>
       <c r="F149" s="8"/>
     </row>
-    <row r="150">
+    <row r="150" ht="15.75" customHeight="1">
       <c r="A150" s="8"/>
       <c r="B150" s="15" t="s">
         <v>30</v>
@@ -3775,10 +3770,10 @@
       <c r="E150" s="8"/>
       <c r="F150" s="8"/>
     </row>
-    <row r="151">
+    <row r="151" ht="15.75" customHeight="1">
       <c r="C151" s="20"/>
     </row>
-    <row r="152">
+    <row r="152" ht="15.75" customHeight="1">
       <c r="A152" s="7" t="s">
         <v>57</v>
       </c>
@@ -3788,7 +3783,7 @@
       <c r="E152" s="8"/>
       <c r="F152" s="8"/>
     </row>
-    <row r="153">
+    <row r="153" ht="15.75" customHeight="1">
       <c r="A153" s="8"/>
       <c r="B153" s="8" t="s">
         <v>10</v>
@@ -3800,7 +3795,7 @@
       <c r="E153" s="8"/>
       <c r="F153" s="8"/>
     </row>
-    <row r="154">
+    <row r="154" ht="15.75" customHeight="1">
       <c r="A154" s="8"/>
       <c r="B154" s="8" t="s">
         <v>12</v>
@@ -3812,7 +3807,7 @@
       <c r="E154" s="8"/>
       <c r="F154" s="8"/>
     </row>
-    <row r="155">
+    <row r="155" ht="15.75" customHeight="1">
       <c r="A155" s="9"/>
       <c r="B155" s="9" t="s">
         <v>2</v>
@@ -3824,7 +3819,7 @@
       <c r="E155" s="6"/>
       <c r="F155" s="8"/>
     </row>
-    <row r="156">
+    <row r="156" ht="15.75" customHeight="1">
       <c r="A156" s="8"/>
       <c r="B156" s="8" t="s">
         <v>19</v>
@@ -3836,7 +3831,7 @@
       <c r="E156" s="8"/>
       <c r="F156" s="8"/>
     </row>
-    <row r="157">
+    <row r="157" ht="15.75" customHeight="1">
       <c r="A157" s="8"/>
       <c r="B157" s="8" t="s">
         <v>20</v>
@@ -3848,7 +3843,7 @@
       <c r="E157" s="8"/>
       <c r="F157" s="8"/>
     </row>
-    <row r="158">
+    <row r="158" ht="15.75" customHeight="1">
       <c r="A158" s="8"/>
       <c r="B158" s="8" t="s">
         <v>22</v>
@@ -3860,7 +3855,7 @@
       <c r="E158" s="8"/>
       <c r="F158" s="8"/>
     </row>
-    <row r="159">
+    <row r="159" ht="15.75" customHeight="1">
       <c r="A159" s="8"/>
       <c r="B159" s="8" t="s">
         <v>23</v>
@@ -3872,7 +3867,7 @@
       <c r="E159" s="8"/>
       <c r="F159" s="8"/>
     </row>
-    <row r="160">
+    <row r="160" ht="15.75" customHeight="1">
       <c r="A160" s="8"/>
       <c r="B160" s="8" t="s">
         <v>25</v>
@@ -3884,7 +3879,7 @@
       <c r="E160" s="8"/>
       <c r="F160" s="8"/>
     </row>
-    <row r="161">
+    <row r="161" ht="15.75" customHeight="1">
       <c r="A161" s="8"/>
       <c r="B161" s="9" t="s">
         <v>26</v>
@@ -3896,7 +3891,7 @@
       </c>
       <c r="F161" s="8"/>
     </row>
-    <row r="162">
+    <row r="162" ht="15.75" customHeight="1">
       <c r="A162" s="8"/>
       <c r="B162" s="8" t="s">
         <v>28</v>
@@ -3908,7 +3903,7 @@
       <c r="E162" s="8"/>
       <c r="F162" s="8"/>
     </row>
-    <row r="163">
+    <row r="163" ht="15.75" customHeight="1">
       <c r="A163" s="8"/>
       <c r="B163" s="15" t="s">
         <v>30</v>
@@ -3920,10 +3915,10 @@
       <c r="E163" s="8"/>
       <c r="F163" s="8"/>
     </row>
-    <row r="164">
+    <row r="164" ht="15.75" customHeight="1">
       <c r="C164" s="20"/>
     </row>
-    <row r="165">
+    <row r="165" ht="15.75" customHeight="1">
       <c r="A165" s="12" t="s">
         <v>59</v>
       </c>
@@ -3933,7 +3928,7 @@
       <c r="E165" s="8"/>
       <c r="F165" s="8"/>
     </row>
-    <row r="166">
+    <row r="166" ht="15.75" customHeight="1">
       <c r="A166" s="8"/>
       <c r="B166" s="8" t="s">
         <v>10</v>
@@ -3945,7 +3940,7 @@
       <c r="E166" s="8"/>
       <c r="F166" s="8"/>
     </row>
-    <row r="167">
+    <row r="167" ht="15.75" customHeight="1">
       <c r="A167" s="8"/>
       <c r="B167" s="8" t="s">
         <v>12</v>
@@ -3957,7 +3952,7 @@
       <c r="E167" s="8"/>
       <c r="F167" s="8"/>
     </row>
-    <row r="168">
+    <row r="168" ht="15.75" customHeight="1">
       <c r="A168" s="6"/>
       <c r="B168" s="9" t="s">
         <v>2</v>
@@ -3971,7 +3966,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="169">
+    <row r="169" ht="15.75" customHeight="1">
       <c r="A169" s="8"/>
       <c r="B169" s="9" t="s">
         <v>16</v>
@@ -3985,7 +3980,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="170">
+    <row r="170" ht="15.75" customHeight="1">
       <c r="A170" s="8"/>
       <c r="B170" s="8" t="s">
         <v>19</v>
@@ -3997,7 +3992,7 @@
       <c r="E170" s="8"/>
       <c r="F170" s="8"/>
     </row>
-    <row r="171">
+    <row r="171" ht="15.75" customHeight="1">
       <c r="A171" s="8"/>
       <c r="B171" s="8" t="s">
         <v>20</v>
@@ -4009,7 +4004,7 @@
       <c r="E171" s="8"/>
       <c r="F171" s="8"/>
     </row>
-    <row r="172">
+    <row r="172" ht="15.75" customHeight="1">
       <c r="A172" s="8"/>
       <c r="B172" s="8" t="s">
         <v>22</v>
@@ -4021,7 +4016,7 @@
       <c r="E172" s="8"/>
       <c r="F172" s="8"/>
     </row>
-    <row r="173">
+    <row r="173" ht="15.75" customHeight="1">
       <c r="A173" s="8"/>
       <c r="B173" s="8" t="s">
         <v>23</v>
@@ -4033,7 +4028,7 @@
       <c r="E173" s="8"/>
       <c r="F173" s="8"/>
     </row>
-    <row r="174">
+    <row r="174" ht="15.75" customHeight="1">
       <c r="A174" s="8"/>
       <c r="B174" s="8" t="s">
         <v>25</v>
@@ -4045,7 +4040,7 @@
       <c r="E174" s="8"/>
       <c r="F174" s="8"/>
     </row>
-    <row r="175">
+    <row r="175" ht="15.75" customHeight="1">
       <c r="A175" s="8"/>
       <c r="B175" s="9" t="s">
         <v>26</v>
@@ -4057,7 +4052,7 @@
       </c>
       <c r="F175" s="8"/>
     </row>
-    <row r="176">
+    <row r="176" ht="15.75" customHeight="1">
       <c r="A176" s="8"/>
       <c r="B176" s="8" t="s">
         <v>28</v>
@@ -4069,7 +4064,7 @@
       <c r="E176" s="8"/>
       <c r="F176" s="8"/>
     </row>
-    <row r="177">
+    <row r="177" ht="15.75" customHeight="1">
       <c r="A177" s="8"/>
       <c r="B177" s="15" t="s">
         <v>30</v>
@@ -4081,7 +4076,7 @@
       <c r="E177" s="8"/>
       <c r="F177" s="8"/>
     </row>
-    <row r="178">
+    <row r="178" ht="15.75" customHeight="1">
       <c r="A178" s="8"/>
       <c r="B178" s="8"/>
       <c r="C178" s="8"/>
@@ -4089,7 +4084,7 @@
       <c r="E178" s="8"/>
       <c r="F178" s="8"/>
     </row>
-    <row r="179">
+    <row r="179" ht="15.75" customHeight="1">
       <c r="A179" s="12" t="s">
         <v>62</v>
       </c>
@@ -4099,7 +4094,7 @@
       <c r="E179" s="8"/>
       <c r="F179" s="8"/>
     </row>
-    <row r="180">
+    <row r="180" ht="15.75" customHeight="1">
       <c r="A180" s="8"/>
       <c r="B180" s="8" t="s">
         <v>10</v>
@@ -4111,7 +4106,7 @@
       <c r="E180" s="8"/>
       <c r="F180" s="8"/>
     </row>
-    <row r="181">
+    <row r="181" ht="15.75" customHeight="1">
       <c r="A181" s="8"/>
       <c r="B181" s="8" t="s">
         <v>12</v>
@@ -4123,7 +4118,7 @@
       <c r="E181" s="8"/>
       <c r="F181" s="8"/>
     </row>
-    <row r="182">
+    <row r="182" ht="15.75" customHeight="1">
       <c r="A182" s="6"/>
       <c r="B182" s="9" t="s">
         <v>2</v>
@@ -4137,7 +4132,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="183">
+    <row r="183" ht="15.75" customHeight="1">
       <c r="A183" s="8"/>
       <c r="B183" s="9" t="s">
         <v>16</v>
@@ -4151,7 +4146,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="184">
+    <row r="184" ht="15.75" customHeight="1">
       <c r="A184" s="8"/>
       <c r="B184" s="8" t="s">
         <v>19</v>
@@ -4163,7 +4158,7 @@
       <c r="E184" s="8"/>
       <c r="F184" s="8"/>
     </row>
-    <row r="185">
+    <row r="185" ht="15.75" customHeight="1">
       <c r="A185" s="8"/>
       <c r="B185" s="8" t="s">
         <v>20</v>
@@ -4175,7 +4170,7 @@
       <c r="E185" s="8"/>
       <c r="F185" s="8"/>
     </row>
-    <row r="186">
+    <row r="186" ht="15.75" customHeight="1">
       <c r="A186" s="8"/>
       <c r="B186" s="8" t="s">
         <v>22</v>
@@ -4187,7 +4182,7 @@
       <c r="E186" s="8"/>
       <c r="F186" s="8"/>
     </row>
-    <row r="187">
+    <row r="187" ht="15.75" customHeight="1">
       <c r="A187" s="8"/>
       <c r="B187" s="8" t="s">
         <v>23</v>
@@ -4199,7 +4194,7 @@
       <c r="E187" s="8"/>
       <c r="F187" s="8"/>
     </row>
-    <row r="188">
+    <row r="188" ht="15.75" customHeight="1">
       <c r="A188" s="8"/>
       <c r="B188" s="8" t="s">
         <v>25</v>
@@ -4211,7 +4206,7 @@
       <c r="E188" s="8"/>
       <c r="F188" s="8"/>
     </row>
-    <row r="189">
+    <row r="189" ht="15.75" customHeight="1">
       <c r="A189" s="8"/>
       <c r="B189" s="9" t="s">
         <v>26</v>
@@ -4223,7 +4218,7 @@
       </c>
       <c r="F189" s="8"/>
     </row>
-    <row r="190">
+    <row r="190" ht="15.75" customHeight="1">
       <c r="A190" s="8"/>
       <c r="B190" s="8" t="s">
         <v>28</v>
@@ -4235,7 +4230,7 @@
       <c r="E190" s="8"/>
       <c r="F190" s="8"/>
     </row>
-    <row r="191">
+    <row r="191" ht="15.75" customHeight="1">
       <c r="A191" s="8"/>
       <c r="B191" s="15" t="s">
         <v>30</v>
@@ -4247,7 +4242,7 @@
       <c r="E191" s="8"/>
       <c r="F191" s="8"/>
     </row>
-    <row r="192">
+    <row r="192" ht="15.75" customHeight="1">
       <c r="A192" s="8"/>
       <c r="B192" s="8"/>
       <c r="C192" s="6"/>
@@ -4255,7 +4250,7 @@
       <c r="E192" s="8"/>
       <c r="F192" s="8"/>
     </row>
-    <row r="193">
+    <row r="193" ht="15.75" customHeight="1">
       <c r="A193" s="12" t="s">
         <v>64</v>
       </c>
@@ -4265,7 +4260,7 @@
       <c r="E193" s="8"/>
       <c r="F193" s="8"/>
     </row>
-    <row r="194">
+    <row r="194" ht="15.75" customHeight="1">
       <c r="A194" s="8"/>
       <c r="B194" s="8" t="s">
         <v>10</v>
@@ -4277,7 +4272,7 @@
       <c r="E194" s="8"/>
       <c r="F194" s="8"/>
     </row>
-    <row r="195">
+    <row r="195" ht="15.75" customHeight="1">
       <c r="A195" s="8"/>
       <c r="B195" s="8" t="s">
         <v>12</v>
@@ -4289,7 +4284,7 @@
       <c r="E195" s="8"/>
       <c r="F195" s="8"/>
     </row>
-    <row r="196">
+    <row r="196" ht="15.75" customHeight="1">
       <c r="A196" s="9"/>
       <c r="B196" s="9" t="s">
         <v>2</v>
@@ -4301,7 +4296,7 @@
       <c r="E196" s="6"/>
       <c r="F196" s="6"/>
     </row>
-    <row r="197">
+    <row r="197" ht="15.75" customHeight="1">
       <c r="A197" s="8"/>
       <c r="B197" s="8" t="s">
         <v>19</v>
@@ -4313,7 +4308,7 @@
       <c r="E197" s="8"/>
       <c r="F197" s="8"/>
     </row>
-    <row r="198">
+    <row r="198" ht="15.75" customHeight="1">
       <c r="A198" s="8"/>
       <c r="B198" s="8" t="s">
         <v>20</v>
@@ -4325,7 +4320,7 @@
       <c r="E198" s="8"/>
       <c r="F198" s="8"/>
     </row>
-    <row r="199">
+    <row r="199" ht="15.75" customHeight="1">
       <c r="A199" s="8"/>
       <c r="B199" s="8" t="s">
         <v>22</v>
@@ -4337,7 +4332,7 @@
       <c r="E199" s="8"/>
       <c r="F199" s="8"/>
     </row>
-    <row r="200">
+    <row r="200" ht="15.75" customHeight="1">
       <c r="A200" s="8"/>
       <c r="B200" s="8" t="s">
         <v>23</v>
@@ -4349,7 +4344,7 @@
       <c r="E200" s="8"/>
       <c r="F200" s="8"/>
     </row>
-    <row r="201">
+    <row r="201" ht="15.75" customHeight="1">
       <c r="A201" s="8"/>
       <c r="B201" s="8" t="s">
         <v>25</v>
@@ -4361,7 +4356,7 @@
       <c r="E201" s="8"/>
       <c r="F201" s="8"/>
     </row>
-    <row r="202">
+    <row r="202" ht="15.75" customHeight="1">
       <c r="A202" s="8"/>
       <c r="B202" s="9" t="s">
         <v>26</v>
@@ -4373,7 +4368,7 @@
       </c>
       <c r="F202" s="8"/>
     </row>
-    <row r="203">
+    <row r="203" ht="15.75" customHeight="1">
       <c r="A203" s="8"/>
       <c r="B203" s="8" t="s">
         <v>28</v>
@@ -4385,7 +4380,7 @@
       <c r="E203" s="8"/>
       <c r="F203" s="8"/>
     </row>
-    <row r="204">
+    <row r="204" ht="15.75" customHeight="1">
       <c r="A204" s="8"/>
       <c r="B204" s="15" t="s">
         <v>30</v>
@@ -4397,7 +4392,7 @@
       <c r="E204" s="8"/>
       <c r="F204" s="8"/>
     </row>
-    <row r="205">
+    <row r="205" ht="15.75" customHeight="1">
       <c r="A205" s="8"/>
       <c r="B205" s="8"/>
       <c r="C205" s="8"/>
@@ -4405,7 +4400,7 @@
       <c r="E205" s="8"/>
       <c r="F205" s="8"/>
     </row>
-    <row r="206">
+    <row r="206" ht="15.75" customHeight="1">
       <c r="A206" s="12" t="s">
         <v>66</v>
       </c>
@@ -4415,7 +4410,7 @@
       <c r="E206" s="8"/>
       <c r="F206" s="8"/>
     </row>
-    <row r="207">
+    <row r="207" ht="15.75" customHeight="1">
       <c r="A207" s="8"/>
       <c r="B207" s="8" t="s">
         <v>10</v>
@@ -4427,7 +4422,7 @@
       <c r="E207" s="8"/>
       <c r="F207" s="8"/>
     </row>
-    <row r="208">
+    <row r="208" ht="15.75" customHeight="1">
       <c r="A208" s="8"/>
       <c r="B208" s="8" t="s">
         <v>12</v>
@@ -4439,7 +4434,7 @@
       <c r="E208" s="8"/>
       <c r="F208" s="8"/>
     </row>
-    <row r="209">
+    <row r="209" ht="15.75" customHeight="1">
       <c r="A209" s="9"/>
       <c r="B209" s="9" t="s">
         <v>2</v>
@@ -4451,7 +4446,7 @@
       <c r="E209" s="6"/>
       <c r="F209" s="8"/>
     </row>
-    <row r="210">
+    <row r="210" ht="15.75" customHeight="1">
       <c r="A210" s="8"/>
       <c r="B210" s="8" t="s">
         <v>19</v>
@@ -4463,7 +4458,7 @@
       <c r="E210" s="8"/>
       <c r="F210" s="8"/>
     </row>
-    <row r="211">
+    <row r="211" ht="15.75" customHeight="1">
       <c r="A211" s="8"/>
       <c r="B211" s="8" t="s">
         <v>20</v>
@@ -4475,7 +4470,7 @@
       <c r="E211" s="8"/>
       <c r="F211" s="8"/>
     </row>
-    <row r="212">
+    <row r="212" ht="15.75" customHeight="1">
       <c r="A212" s="8"/>
       <c r="B212" s="8" t="s">
         <v>22</v>
@@ -4487,7 +4482,7 @@
       <c r="E212" s="8"/>
       <c r="F212" s="8"/>
     </row>
-    <row r="213">
+    <row r="213" ht="15.75" customHeight="1">
       <c r="A213" s="8"/>
       <c r="B213" s="8" t="s">
         <v>23</v>
@@ -4499,7 +4494,7 @@
       <c r="E213" s="8"/>
       <c r="F213" s="8"/>
     </row>
-    <row r="214">
+    <row r="214" ht="15.75" customHeight="1">
       <c r="A214" s="8"/>
       <c r="B214" s="8" t="s">
         <v>25</v>
@@ -4511,7 +4506,7 @@
       <c r="E214" s="8"/>
       <c r="F214" s="8"/>
     </row>
-    <row r="215">
+    <row r="215" ht="15.75" customHeight="1">
       <c r="A215" s="8"/>
       <c r="B215" s="9" t="s">
         <v>26</v>
@@ -4523,7 +4518,7 @@
       </c>
       <c r="F215" s="8"/>
     </row>
-    <row r="216">
+    <row r="216" ht="15.75" customHeight="1">
       <c r="A216" s="8"/>
       <c r="B216" s="8" t="s">
         <v>28</v>
@@ -4535,7 +4530,7 @@
       <c r="E216" s="8"/>
       <c r="F216" s="8"/>
     </row>
-    <row r="217">
+    <row r="217" ht="15.75" customHeight="1">
       <c r="A217" s="8"/>
       <c r="B217" s="15" t="s">
         <v>30</v>
@@ -4547,17 +4542,17 @@
       <c r="E217" s="8"/>
       <c r="F217" s="8"/>
     </row>
-    <row r="218">
+    <row r="218" ht="15.75" customHeight="1">
       <c r="C218" s="20"/>
     </row>
-    <row r="219">
+    <row r="219" ht="15.75" customHeight="1">
       <c r="A219" s="15" t="s">
         <v>68</v>
       </c>
       <c r="B219" s="15"/>
       <c r="C219" s="6"/>
     </row>
-    <row r="220">
+    <row r="220" ht="15.75" customHeight="1">
       <c r="A220" s="15"/>
       <c r="B220" s="15" t="s">
         <v>10</v>
@@ -4566,7 +4561,7 @@
         <v>69</v>
       </c>
     </row>
-    <row r="221">
+    <row r="221" ht="15.75" customHeight="1">
       <c r="A221" s="15"/>
       <c r="B221" s="15" t="s">
         <v>12</v>
@@ -4575,7 +4570,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="222">
+    <row r="222" ht="15.75" customHeight="1">
       <c r="A222" s="15"/>
       <c r="B222" s="15" t="s">
         <v>2</v>
@@ -4586,7 +4581,7 @@
       <c r="D222" s="6"/>
       <c r="E222" s="6"/>
     </row>
-    <row r="223">
+    <row r="223" ht="15.75" customHeight="1">
       <c r="A223" s="15"/>
       <c r="B223" s="15" t="s">
         <v>19</v>
@@ -4595,7 +4590,7 @@
       <c r="D223" s="8"/>
       <c r="E223" s="8"/>
     </row>
-    <row r="224">
+    <row r="224" ht="15.75" customHeight="1">
       <c r="A224" s="15"/>
       <c r="B224" s="15" t="s">
         <v>20</v>
@@ -4604,7 +4599,7 @@
         <v>70</v>
       </c>
     </row>
-    <row r="225">
+    <row r="225" ht="15.75" customHeight="1">
       <c r="A225" s="15"/>
       <c r="B225" s="8" t="s">
         <v>71</v>
@@ -4613,7 +4608,7 @@
         <v>72</v>
       </c>
     </row>
-    <row r="226">
+    <row r="226" ht="15.75" customHeight="1">
       <c r="A226" s="15"/>
       <c r="B226" s="6" t="s">
         <v>73</v>
@@ -4622,19 +4617,19 @@
         <v>74</v>
       </c>
     </row>
-    <row r="227">
+    <row r="227" ht="15.75" customHeight="1">
       <c r="A227" s="2"/>
       <c r="B227" s="2"/>
       <c r="C227" s="27"/>
     </row>
-    <row r="228">
+    <row r="228" ht="15.75" customHeight="1">
       <c r="A228" s="16" t="s">
         <v>75</v>
       </c>
       <c r="B228" s="2"/>
       <c r="C228" s="19"/>
     </row>
-    <row r="229">
+    <row r="229" ht="15.75" customHeight="1">
       <c r="A229" s="2"/>
       <c r="B229" s="2" t="s">
         <v>10</v>
@@ -4643,7 +4638,7 @@
         <v>69</v>
       </c>
     </row>
-    <row r="230">
+    <row r="230" ht="15.75" customHeight="1">
       <c r="A230" s="2"/>
       <c r="B230" s="2" t="s">
         <v>12</v>
@@ -4652,7 +4647,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="231">
+    <row r="231" ht="15.75" customHeight="1">
       <c r="A231" s="2"/>
       <c r="B231" s="2" t="s">
         <v>2</v>
@@ -4661,14 +4656,14 @@
         <v>1.0</v>
       </c>
     </row>
-    <row r="232">
+    <row r="232" ht="15.75" customHeight="1">
       <c r="A232" s="2"/>
       <c r="B232" s="2" t="s">
         <v>19</v>
       </c>
       <c r="C232" s="28"/>
     </row>
-    <row r="233">
+    <row r="233" ht="15.75" customHeight="1">
       <c r="A233" s="2"/>
       <c r="B233" s="2" t="s">
         <v>20</v>
@@ -4677,7 +4672,7 @@
         <v>76</v>
       </c>
     </row>
-    <row r="234">
+    <row r="234" ht="15.75" customHeight="1">
       <c r="A234" s="2"/>
       <c r="B234" s="8" t="s">
         <v>71</v>
@@ -4686,7 +4681,7 @@
         <v>72</v>
       </c>
     </row>
-    <row r="235">
+    <row r="235" ht="15.75" customHeight="1">
       <c r="A235" s="2"/>
       <c r="B235" s="6" t="s">
         <v>73</v>
@@ -4695,19 +4690,19 @@
         <v>74</v>
       </c>
     </row>
-    <row r="236">
+    <row r="236" ht="15.75" customHeight="1">
       <c r="A236" s="2"/>
       <c r="B236" s="2"/>
       <c r="C236" s="19"/>
     </row>
-    <row r="237">
+    <row r="237" ht="15.75" customHeight="1">
       <c r="A237" s="16" t="s">
         <v>77</v>
       </c>
       <c r="B237" s="2"/>
       <c r="C237" s="19"/>
     </row>
-    <row r="238">
+    <row r="238" ht="15.75" customHeight="1">
       <c r="A238" s="2"/>
       <c r="B238" s="2" t="s">
         <v>10</v>
@@ -4716,7 +4711,7 @@
         <v>69</v>
       </c>
     </row>
-    <row r="239">
+    <row r="239" ht="15.75" customHeight="1">
       <c r="A239" s="2"/>
       <c r="B239" s="2" t="s">
         <v>12</v>
@@ -4725,7 +4720,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="240">
+    <row r="240" ht="15.75" customHeight="1">
       <c r="A240" s="2"/>
       <c r="B240" s="2" t="s">
         <v>2</v>
@@ -4734,14 +4729,14 @@
         <v>1.0</v>
       </c>
     </row>
-    <row r="241">
+    <row r="241" ht="15.75" customHeight="1">
       <c r="A241" s="2"/>
       <c r="B241" s="2" t="s">
         <v>19</v>
       </c>
       <c r="C241" s="28"/>
     </row>
-    <row r="242">
+    <row r="242" ht="15.75" customHeight="1">
       <c r="A242" s="2"/>
       <c r="B242" s="2" t="s">
         <v>20</v>
@@ -4750,7 +4745,7 @@
         <v>78</v>
       </c>
     </row>
-    <row r="243">
+    <row r="243" ht="15.75" customHeight="1">
       <c r="A243" s="2"/>
       <c r="B243" s="8" t="s">
         <v>71</v>
@@ -4759,7 +4754,7 @@
         <v>72</v>
       </c>
     </row>
-    <row r="244">
+    <row r="244" ht="15.75" customHeight="1">
       <c r="A244" s="2"/>
       <c r="B244" s="6" t="s">
         <v>73</v>
@@ -4768,10 +4763,10 @@
         <v>74</v>
       </c>
     </row>
-    <row r="245">
+    <row r="245" ht="15.75" customHeight="1">
       <c r="C245" s="20"/>
     </row>
-    <row r="246">
+    <row r="246" ht="15.75" customHeight="1">
       <c r="A246" s="8" t="s">
         <v>79</v>
       </c>
@@ -4779,7 +4774,7 @@
       <c r="C246" s="6"/>
       <c r="D246" s="8"/>
     </row>
-    <row r="247">
+    <row r="247" ht="15.75" customHeight="1">
       <c r="A247" s="8"/>
       <c r="B247" s="8" t="s">
         <v>10</v>
@@ -4789,7 +4784,7 @@
       </c>
       <c r="D247" s="8"/>
     </row>
-    <row r="248">
+    <row r="248" ht="15.75" customHeight="1">
       <c r="A248" s="8"/>
       <c r="B248" s="8" t="s">
         <v>12</v>
@@ -4799,7 +4794,7 @@
       </c>
       <c r="D248" s="8"/>
     </row>
-    <row r="249">
+    <row r="249" ht="15.75" customHeight="1">
       <c r="A249" s="8"/>
       <c r="B249" s="8" t="s">
         <v>2</v>
@@ -4809,7 +4804,7 @@
       </c>
       <c r="D249" s="8"/>
     </row>
-    <row r="250">
+    <row r="250" ht="15.75" customHeight="1">
       <c r="A250" s="8"/>
       <c r="B250" s="8" t="s">
         <v>19</v>
@@ -4817,7 +4812,7 @@
       <c r="C250" s="9"/>
       <c r="D250" s="8"/>
     </row>
-    <row r="251">
+    <row r="251" ht="15.75" customHeight="1">
       <c r="A251" s="8"/>
       <c r="B251" s="8" t="s">
         <v>20</v>
@@ -4827,7 +4822,7 @@
       </c>
       <c r="D251" s="8"/>
     </row>
-    <row r="252">
+    <row r="252" ht="15.75" customHeight="1">
       <c r="A252" s="8"/>
       <c r="B252" s="8" t="s">
         <v>71</v>
@@ -4837,7 +4832,7 @@
       </c>
       <c r="D252" s="8"/>
     </row>
-    <row r="253">
+    <row r="253" ht="15.75" customHeight="1">
       <c r="A253" s="8"/>
       <c r="B253" s="6" t="s">
         <v>73</v>
